--- a/resources/rtgs_transactions.xlsx
+++ b/resources/rtgs_transactions.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,30 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EBF3FB"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -56,31 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00AAAAAA"/>
-      </left>
-      <right style="thin">
-        <color rgb="00AAAAAA"/>
-      </right>
-      <top style="thin">
-        <color rgb="00AAAAAA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00AAAAAA"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,240 +413,830 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>txnType</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>incomingTnxId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>sourceSystemId</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>transactionType</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>channelType</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fromBankName</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>toBankName</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>fromBankCode</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>toBankCode</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>nostroAccount</t>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>processingStatus</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ingestionTimeStamp</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>batchId</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>creditAccountId</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>debitAccountId</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>originalTransactionId</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>reversalType</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>nostroAccountId</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>vostroAccountId</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>internalRef</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>processingNode</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>rbiCode</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>3001</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>CREDIT</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>SBI01</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>HDFC02</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>NOSTRO_SBI_HDFC</t>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>RTGS</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SBI</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>HDFC</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>RECEIVED</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2025-04-09T09:00:00</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>6001</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>RTG-001</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>NODE-A</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>RBI001</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
+      <c r="A3" t="n">
+        <v>3002</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CREDIT</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>RTGS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ICICI</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>2500000</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>HDFC02</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>SBI01</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>NOSTRO_HDFC_SBI</t>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>RECEIVED</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2025-04-09T09:00:00</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>6002</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>RTG-002</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>NODE-B</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>RBI002</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3003</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>CREDIT</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>9000000</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>AXIS03</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>ICIC04</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>NOSTRO_AXIS_ICIC</t>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>RTGS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AXIS</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>BOB</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>750000</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>RECEIVED</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2025-04-09T09:00:00</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>6003</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>RTG-003</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>NODE-A</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>RBI003</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>ICIC04</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>SBI01</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>NOSTRO_ICIC_SBI</t>
+      <c r="A5" t="n">
+        <v>3004</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CREDIT</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>RTGS</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>KOTAK</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>RECEIVED</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2025-04-09T09:00:00</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>6004</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>RTG-004</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>NODE-C</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>RBI004</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CREDIT</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>7500000</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>SBI01</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>AXIS03</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>NOSTRO_SBI_AXIS</t>
+      <c r="A6" t="n">
+        <v>3005</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RTGS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HDFC</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SBI</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>900000</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>RECEIVED</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2025-04-09T09:00:00</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>7001</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>RTG-005</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>NODE-B</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>RBI005</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>REVERSAL</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>HDFC02</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>SBI01</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>NOSTRO_HDFC_SBI</t>
+      <c r="A7" t="n">
+        <v>3006</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RTGS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ICICI</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>RECEIVED</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2025-04-09T09:00:00</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>7002</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>RTG-006</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>NODE-A</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>RBI006</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CREDIT</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>ICIC04</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>HDFC02</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>NOSTRO_ICIC_HDFC</t>
+      <c r="A8" t="n">
+        <v>3007</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RTGS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>BOB</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>AXIS</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>650000</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>RECEIVED</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2025-04-09T09:00:00</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>7003</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>RTG-007</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>NODE-C</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>RBI007</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>AXIS03</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>SBI01</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>NOSTRO_AXIS_SBI</t>
+      <c r="A9" t="n">
+        <v>3008</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>REVERSAL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RTGS</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SBI</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>HDFC</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>RECEIVED</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2025-04-09T09:00:00</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>3001</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>RTG-008</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>NODE-A</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>RBI008</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3009</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>REVERSAL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>RTGS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ICICI</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1250000</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>RECEIVED</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2025-04-09T09:00:00</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>3002</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>RTG-009</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>NODE-B</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>RBI009</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3010</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>INTRABANK</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>INTERNAL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SBI</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>HDFC</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>RECEIVED</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2025-04-09T09:00:00</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>8001</v>
+      </c>
+      <c r="P11" t="n">
+        <v>9001</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>RTG-010</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>NODE-A</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>RBI010</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3011</v>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>INTRABANK</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>INTERNAL</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ICICI</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AXIS</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>RECEIVED</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2025-04-09T09:00:00</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>8002</v>
+      </c>
+      <c r="P12" t="n">
+        <v>9002</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>RTG-011</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>NODE-C</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>RBI011</t>
         </is>
       </c>
     </row>
